--- a/content/templates/files/first-sale-math/127-first-sale-math.xlsx
+++ b/content/templates/files/first-sale-math/127-first-sale-math.xlsx
@@ -629,7 +629,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1.  Open the Math tab. Fill the white cells for your test price in column B.</t>
+          <t>1.  Open the Math tab. Fill the white cells for your test price in column C.</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5.  Try a lower and a higher price in columns C and D to compare.</t>
+          <t>5.  Try a lower and a higher price in columns B and D to compare.</t>
         </is>
       </c>
     </row>
